--- a/lca/results/lca_results_regionalized.xlsx
+++ b/lca/results/lca_results_regionalized.xlsx
@@ -358,6 +358,9 @@
     <t>MZ</t>
   </si>
   <si>
+    <t>NA</t>
+  </si>
+  <si>
     <t>NC</t>
   </si>
   <si>
@@ -538,9 +541,6 @@
     <t>ZW</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>United Arab Emirates</t>
   </si>
   <si>
@@ -865,6 +865,9 @@
     <t>Mozambique</t>
   </si>
   <si>
+    <t>Namibia</t>
+  </si>
+  <si>
     <t>New Caledonia</t>
   </si>
   <si>
@@ -1043,9 +1046,6 @@
   </si>
   <si>
     <t>Zimbabwe</t>
-  </si>
-  <si>
-    <t>Namibia</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1434,7 @@
         <v>175</v>
       </c>
       <c r="C2">
-        <v>7.190540329255186</v>
+        <v>2.731841351645488</v>
       </c>
       <c r="D2">
         <v>0.8147387379957454</v>
@@ -1454,7 +1454,7 @@
         <v>176</v>
       </c>
       <c r="C3">
-        <v>8.914975203052501</v>
+        <v>3.268914796467869</v>
       </c>
       <c r="D3">
         <v>0.9011618643111927</v>
@@ -1474,7 +1474,7 @@
         <v>177</v>
       </c>
       <c r="C4">
-        <v>2.849443713451062</v>
+        <v>1.948951919240298</v>
       </c>
       <c r="D4">
         <v>0.7526952848924106</v>
@@ -1494,7 +1494,7 @@
         <v>178</v>
       </c>
       <c r="C5">
-        <v>4.992461012482819</v>
+        <v>2.619774980197401</v>
       </c>
       <c r="D5">
         <v>0.7996513071404514</v>
@@ -1503,7 +1503,7 @@
         <v>3.48036771810146</v>
       </c>
       <c r="F5">
-        <v>0.8644342773270363</v>
+        <v>0.8644342773270361</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1514,7 +1514,7 @@
         <v>179</v>
       </c>
       <c r="C6">
-        <v>4.470358496967132</v>
+        <v>2.45190307960343</v>
       </c>
       <c r="D6">
         <v>0.847948542699406</v>
@@ -1534,7 +1534,7 @@
         <v>180</v>
       </c>
       <c r="C7">
-        <v>5.224996877907868</v>
+        <v>2.257810395647165</v>
       </c>
       <c r="D7">
         <v>0.6909829946457154</v>
@@ -1554,7 +1554,7 @@
         <v>181</v>
       </c>
       <c r="C8">
-        <v>3.419566714744598</v>
+        <v>1.627366398239341</v>
       </c>
       <c r="D8">
         <v>0.7857633784893012</v>
@@ -1574,7 +1574,7 @@
         <v>182</v>
       </c>
       <c r="C9">
-        <v>9.080919161438441</v>
+        <v>2.705205656146799</v>
       </c>
       <c r="D9">
         <v>0.8447709430369323</v>
@@ -1594,7 +1594,7 @@
         <v>183</v>
       </c>
       <c r="C10">
-        <v>7.69473950461082</v>
+        <v>3.055295434147538</v>
       </c>
       <c r="D10">
         <v>1.260245426076748</v>
@@ -1614,7 +1614,7 @@
         <v>184</v>
       </c>
       <c r="C11">
-        <v>8.871849530676691</v>
+        <v>2.915940800567262</v>
       </c>
       <c r="D11">
         <v>0.8257976258025905</v>
@@ -1634,7 +1634,7 @@
         <v>185</v>
       </c>
       <c r="C12">
-        <v>8.84045096143295</v>
+        <v>3.063009311198036</v>
       </c>
       <c r="D12">
         <v>0.9014987580914567</v>
@@ -1654,7 +1654,7 @@
         <v>186</v>
       </c>
       <c r="C13">
-        <v>3.274601291095929</v>
+        <v>1.587520879724128</v>
       </c>
       <c r="D13">
         <v>0.6854386115050309</v>
@@ -1663,7 +1663,7 @@
         <v>3.039259100362067</v>
       </c>
       <c r="F13">
-        <v>0.7472600261772617</v>
+        <v>0.7472600261772615</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1674,10 +1674,10 @@
         <v>187</v>
       </c>
       <c r="C14">
-        <v>8.504449469990275</v>
+        <v>3.186734637644529</v>
       </c>
       <c r="D14">
-        <v>0.8951036819761801</v>
+        <v>0.8951036819761802</v>
       </c>
       <c r="E14">
         <v>3.531540867304834</v>
@@ -1694,10 +1694,10 @@
         <v>188</v>
       </c>
       <c r="C15">
-        <v>5.568060975541163</v>
+        <v>2.047191469909508</v>
       </c>
       <c r="D15">
-        <v>0.8459800999481225</v>
+        <v>0.8459800999481224</v>
       </c>
       <c r="E15">
         <v>4.081464496879819</v>
@@ -1714,7 +1714,7 @@
         <v>189</v>
       </c>
       <c r="C16">
-        <v>8.408220767755598</v>
+        <v>3.185720080574611</v>
       </c>
       <c r="D16">
         <v>0.8951036819761801</v>
@@ -1723,7 +1723,7 @@
         <v>3.531540867304834</v>
       </c>
       <c r="F16">
-        <v>0.9591089364530876</v>
+        <v>0.9591089364530877</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1734,10 +1734,10 @@
         <v>190</v>
       </c>
       <c r="C17">
-        <v>8.083893824217286</v>
+        <v>3.120045779218586</v>
       </c>
       <c r="D17">
-        <v>0.8902592111435085</v>
+        <v>0.8902592111435083</v>
       </c>
       <c r="E17">
         <v>3.525529201581805</v>
@@ -1754,7 +1754,7 @@
         <v>191</v>
       </c>
       <c r="C18">
-        <v>7.81684141485608</v>
+        <v>2.907959359117275</v>
       </c>
       <c r="D18">
         <v>0.890612683394139</v>
@@ -1774,7 +1774,7 @@
         <v>192</v>
       </c>
       <c r="C19">
-        <v>6.048324155678648</v>
+        <v>2.610292935861608</v>
       </c>
       <c r="D19">
         <v>0.8071930616283736</v>
@@ -1794,7 +1794,7 @@
         <v>193</v>
       </c>
       <c r="C20">
-        <v>3.90123600248954</v>
+        <v>1.995013530837337</v>
       </c>
       <c r="D20">
         <v>0.6730718377328458</v>
@@ -1814,10 +1814,10 @@
         <v>194</v>
       </c>
       <c r="C21">
-        <v>5.827526959226592</v>
+        <v>2.565185534371237</v>
       </c>
       <c r="D21">
-        <v>0.8663403596966338</v>
+        <v>0.8663403596966337</v>
       </c>
       <c r="E21">
         <v>3.645751560103559</v>
@@ -1834,7 +1834,7 @@
         <v>195</v>
       </c>
       <c r="C22">
-        <v>8.703214170356667</v>
+        <v>3.057153763772041</v>
       </c>
       <c r="D22">
         <v>0.901160951471191</v>
@@ -1854,7 +1854,7 @@
         <v>196</v>
       </c>
       <c r="C23">
-        <v>12.02182695376253</v>
+        <v>3.764302234761073</v>
       </c>
       <c r="D23">
         <v>0.9371623287667321</v>
@@ -1874,7 +1874,7 @@
         <v>197</v>
       </c>
       <c r="C24">
-        <v>7.69256995319144</v>
+        <v>2.757774247412757</v>
       </c>
       <c r="D24">
         <v>0.8492337265142599</v>
@@ -1894,7 +1894,7 @@
         <v>198</v>
       </c>
       <c r="C25">
-        <v>6.00345728713037</v>
+        <v>2.790926072617118</v>
       </c>
       <c r="D25">
         <v>0.8663550522189059</v>
@@ -1914,7 +1914,7 @@
         <v>199</v>
       </c>
       <c r="C26">
-        <v>3.795709931191198</v>
+        <v>2.1317082727673</v>
       </c>
       <c r="D26">
         <v>0.7911995283983749</v>
@@ -1934,7 +1934,7 @@
         <v>200</v>
       </c>
       <c r="C27">
-        <v>2.848559811550532</v>
+        <v>2.189211956779375</v>
       </c>
       <c r="D27">
         <v>0.8288298333406812</v>
@@ -1954,7 +1954,7 @@
         <v>201</v>
       </c>
       <c r="C28">
-        <v>8.473669277189664</v>
+        <v>3.186410116358321</v>
       </c>
       <c r="D28">
         <v>0.8951036819761801</v>
@@ -1974,7 +1974,7 @@
         <v>202</v>
       </c>
       <c r="C29">
-        <v>2.7295547694694</v>
+        <v>2.180285826200234</v>
       </c>
       <c r="D29">
         <v>0.8282325949001913</v>
@@ -1994,10 +1994,10 @@
         <v>203</v>
       </c>
       <c r="C30">
-        <v>2.075552312697071</v>
+        <v>1.457949572155041</v>
       </c>
       <c r="D30">
-        <v>0.7469344648191669</v>
+        <v>0.7469344648191668</v>
       </c>
       <c r="E30">
         <v>3.354797448580654</v>
@@ -2014,7 +2014,7 @@
         <v>204</v>
       </c>
       <c r="C31">
-        <v>6.841821557664667</v>
+        <v>2.914799219262088</v>
       </c>
       <c r="D31">
         <v>0.8753064274697837</v>
@@ -2034,7 +2034,7 @@
         <v>205</v>
       </c>
       <c r="C32">
-        <v>6.197031320806462</v>
+        <v>2.265304085495507</v>
       </c>
       <c r="D32">
         <v>0.7846914057349119</v>
@@ -2054,7 +2054,7 @@
         <v>206</v>
       </c>
       <c r="C33">
-        <v>3.193631165677485</v>
+        <v>2.319588754838211</v>
       </c>
       <c r="D33">
         <v>0.8317975648130633</v>
@@ -2074,7 +2074,7 @@
         <v>207</v>
       </c>
       <c r="C34">
-        <v>8.629295051945892</v>
+        <v>2.957759580113001</v>
       </c>
       <c r="D34">
         <v>1.246428113450369</v>
@@ -2094,7 +2094,7 @@
         <v>208</v>
       </c>
       <c r="C35">
-        <v>4.130087443139624</v>
+        <v>1.83811899825169</v>
       </c>
       <c r="D35">
         <v>0.788417413030818</v>
@@ -2114,7 +2114,7 @@
         <v>209</v>
       </c>
       <c r="C36">
-        <v>2.755004086067143</v>
+        <v>2.044566630958518</v>
       </c>
       <c r="D36">
         <v>0.8295119238802943</v>
@@ -2134,7 +2134,7 @@
         <v>210</v>
       </c>
       <c r="C37">
-        <v>10.6071637326983</v>
+        <v>3.546724193201085</v>
       </c>
       <c r="D37">
         <v>0.9213917546560202</v>
@@ -2154,7 +2154,7 @@
         <v>211</v>
       </c>
       <c r="C38">
-        <v>10.76499723558059</v>
+        <v>3.51852188855326</v>
       </c>
       <c r="D38">
         <v>0.9241351534391293</v>
@@ -2163,7 +2163,7 @@
         <v>3.98266789638451</v>
       </c>
       <c r="F38">
-        <v>0.9913399388132136</v>
+        <v>0.9913399388132134</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2174,7 +2174,7 @@
         <v>212</v>
       </c>
       <c r="C39">
-        <v>6.630458548967016</v>
+        <v>2.305999186165552</v>
       </c>
       <c r="D39">
         <v>0.8428094669550971</v>
@@ -2183,7 +2183,7 @@
         <v>4.329826500088498</v>
       </c>
       <c r="F39">
-        <v>0.912998367496468</v>
+        <v>0.9129983674964681</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2194,7 +2194,7 @@
         <v>213</v>
       </c>
       <c r="C40">
-        <v>4.828325848584262</v>
+        <v>1.866274061690391</v>
       </c>
       <c r="D40">
         <v>0.741150439767692</v>
@@ -2203,7 +2203,7 @@
         <v>3.121937952656719</v>
       </c>
       <c r="F40">
-        <v>0.8036576308134009</v>
+        <v>0.8036576308134011</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2214,13 +2214,13 @@
         <v>214</v>
       </c>
       <c r="C41">
-        <v>8.193930003943615</v>
+        <v>2.971429316762634</v>
       </c>
       <c r="D41">
         <v>0.895100375568186</v>
       </c>
       <c r="E41">
-        <v>3.662511165532919</v>
+        <v>3.662511165532918</v>
       </c>
       <c r="F41">
         <v>0.9601388698838199</v>
@@ -2234,7 +2234,7 @@
         <v>215</v>
       </c>
       <c r="C42">
-        <v>2.92820329319339</v>
+        <v>1.536504222689739</v>
       </c>
       <c r="D42">
         <v>0.7282640878963422</v>
@@ -2243,7 +2243,7 @@
         <v>2.75476853900165</v>
       </c>
       <c r="F42">
-        <v>0.7874453901054488</v>
+        <v>0.7874453901054489</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2254,7 +2254,7 @@
         <v>216</v>
       </c>
       <c r="C43">
-        <v>8.523435677335726</v>
+        <v>3.013718684964704</v>
       </c>
       <c r="D43">
         <v>0.8980281677771177</v>
@@ -2274,7 +2274,7 @@
         <v>217</v>
       </c>
       <c r="C44">
-        <v>7.903255431043112</v>
+        <v>2.916483855372054</v>
       </c>
       <c r="D44">
         <v>0.8296560511329983</v>
@@ -2294,7 +2294,7 @@
         <v>218</v>
       </c>
       <c r="C45">
-        <v>3.47583497164932</v>
+        <v>2.290786839415761</v>
       </c>
       <c r="D45">
         <v>0.7740320706589952</v>
@@ -2314,7 +2314,7 @@
         <v>219</v>
       </c>
       <c r="C46">
-        <v>4.457781259634218</v>
+        <v>1.828732554057188</v>
       </c>
       <c r="D46">
         <v>0.7689408363436043</v>
@@ -2334,7 +2334,7 @@
         <v>220</v>
       </c>
       <c r="C47">
-        <v>7.334398970177195</v>
+        <v>2.821946019405202</v>
       </c>
       <c r="D47">
         <v>0.8199948590675262</v>
@@ -2354,7 +2354,7 @@
         <v>221</v>
       </c>
       <c r="C48">
-        <v>10.74096468037467</v>
+        <v>3.56869051663674</v>
       </c>
       <c r="D48">
         <v>0.9229913273112571</v>
@@ -2374,7 +2374,7 @@
         <v>222</v>
       </c>
       <c r="C49">
-        <v>3.22010547565709</v>
+        <v>1.563415794287921</v>
       </c>
       <c r="D49">
         <v>0.7478338633829412</v>
@@ -2383,7 +2383,7 @@
         <v>3.07495555527018</v>
       </c>
       <c r="F49">
-        <v>0.8086792021526029</v>
+        <v>0.8086792021526031</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2394,7 +2394,7 @@
         <v>223</v>
       </c>
       <c r="C50">
-        <v>2.953398903225435</v>
+        <v>2.27587573639706</v>
       </c>
       <c r="D50">
         <v>0.8287778896732544</v>
@@ -2414,7 +2414,7 @@
         <v>224</v>
       </c>
       <c r="C51">
-        <v>2.897299568228406</v>
+        <v>1.545395397009264</v>
       </c>
       <c r="D51">
         <v>0.7923937255372796</v>
@@ -2434,7 +2434,7 @@
         <v>225</v>
       </c>
       <c r="C52">
-        <v>7.740561372703244</v>
+        <v>3.067131479533613</v>
       </c>
       <c r="D52">
         <v>0.8864232749375226</v>
@@ -2454,7 +2454,7 @@
         <v>226</v>
       </c>
       <c r="C53">
-        <v>2.274038527651072</v>
+        <v>1.410805844103705</v>
       </c>
       <c r="D53">
         <v>0.7186853267280506</v>
@@ -2474,7 +2474,7 @@
         <v>227</v>
       </c>
       <c r="C54">
-        <v>5.509367353207542</v>
+        <v>2.696206935771873</v>
       </c>
       <c r="D54">
         <v>0.8593896865215215</v>
@@ -2494,7 +2494,7 @@
         <v>228</v>
       </c>
       <c r="C55">
-        <v>3.592142944989303</v>
+        <v>1.557117042537733</v>
       </c>
       <c r="D55">
         <v>0.7204523143843511</v>
@@ -2514,7 +2514,7 @@
         <v>229</v>
       </c>
       <c r="C56">
-        <v>4.181482797702147</v>
+        <v>2.491809499668056</v>
       </c>
       <c r="D56">
         <v>0.7193132300059976</v>
@@ -2523,7 +2523,7 @@
         <v>3.983182808198706</v>
       </c>
       <c r="F56">
-        <v>0.7890571510097175</v>
+        <v>0.7890571510097174</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2534,7 +2534,7 @@
         <v>230</v>
       </c>
       <c r="C57">
-        <v>6.283896732178532</v>
+        <v>2.824161951087614</v>
       </c>
       <c r="D57">
         <v>0.8685236050164006</v>
@@ -2554,7 +2554,7 @@
         <v>231</v>
       </c>
       <c r="C58">
-        <v>5.84698305735474</v>
+        <v>2.765237438864612</v>
       </c>
       <c r="D58">
         <v>0.8644844234711653</v>
@@ -2574,7 +2574,7 @@
         <v>232</v>
       </c>
       <c r="C59">
-        <v>8.408220767755598</v>
+        <v>3.18572008057461</v>
       </c>
       <c r="D59">
         <v>0.8951036819761802</v>
@@ -2594,7 +2594,7 @@
         <v>233</v>
       </c>
       <c r="C60">
-        <v>8.508784071187332</v>
+        <v>3.18678033814955</v>
       </c>
       <c r="D60">
         <v>0.8951036819761802</v>
@@ -2614,7 +2614,7 @@
         <v>234</v>
       </c>
       <c r="C61">
-        <v>8.408220767755598</v>
+        <v>3.185720080574611</v>
       </c>
       <c r="D61">
         <v>0.8951036819761803</v>
@@ -2634,7 +2634,7 @@
         <v>235</v>
       </c>
       <c r="C62">
-        <v>6.551215074787063</v>
+        <v>2.255854215022914</v>
       </c>
       <c r="D62">
         <v>0.9207843614152031</v>
@@ -2654,7 +2654,7 @@
         <v>236</v>
       </c>
       <c r="C63">
-        <v>5.534463328744695</v>
+        <v>2.512362084947504</v>
       </c>
       <c r="D63">
         <v>0.8625842466465334</v>
@@ -2663,7 +2663,7 @@
         <v>3.959837600406562</v>
       </c>
       <c r="F63">
-        <v>0.930370741670531</v>
+        <v>0.9303707416705309</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2674,10 +2674,10 @@
         <v>237</v>
       </c>
       <c r="C64">
-        <v>8.408220767755598</v>
+        <v>3.185720080574611</v>
       </c>
       <c r="D64">
-        <v>0.8951036819761802</v>
+        <v>0.8951036819761801</v>
       </c>
       <c r="E64">
         <v>3.531540867304834</v>
@@ -2694,7 +2694,7 @@
         <v>238</v>
       </c>
       <c r="C65">
-        <v>6.086368788739937</v>
+        <v>2.791800223968868</v>
       </c>
       <c r="D65">
         <v>0.8663550522189059</v>
@@ -2714,7 +2714,7 @@
         <v>239</v>
       </c>
       <c r="C66">
-        <v>7.268774401746845</v>
+        <v>2.917689247586844</v>
       </c>
       <c r="D66">
         <v>0.8819120367704963</v>
@@ -2734,7 +2734,7 @@
         <v>240</v>
       </c>
       <c r="C67">
-        <v>4.94957958469783</v>
+        <v>2.223592256714388</v>
       </c>
       <c r="D67">
         <v>0.7453446039227682</v>
@@ -2754,7 +2754,7 @@
         <v>241</v>
       </c>
       <c r="C68">
-        <v>11.4517393208473</v>
+        <v>3.68537956790002</v>
       </c>
       <c r="D68">
         <v>0.9314885442494047</v>
@@ -2774,7 +2774,7 @@
         <v>242</v>
       </c>
       <c r="C69">
-        <v>4.395337833258206</v>
+        <v>1.755982776597701</v>
       </c>
       <c r="D69">
         <v>0.8321218386731544</v>
@@ -2794,7 +2794,7 @@
         <v>243</v>
       </c>
       <c r="C70">
-        <v>10.72801139088407</v>
+        <v>2.923322286938456</v>
       </c>
       <c r="D70">
         <v>0.8683257301368816</v>
@@ -2814,7 +2814,7 @@
         <v>244</v>
       </c>
       <c r="C71">
-        <v>4.258438918058143</v>
+        <v>1.735964079533086</v>
       </c>
       <c r="D71">
         <v>0.7790338461070772</v>
@@ -2834,7 +2834,7 @@
         <v>245</v>
       </c>
       <c r="C72">
-        <v>8.494778921542389</v>
+        <v>3.121592563631831</v>
       </c>
       <c r="D72">
         <v>0.8967707758423258</v>
@@ -2854,7 +2854,7 @@
         <v>246</v>
       </c>
       <c r="C73">
-        <v>11.88443684995773</v>
+        <v>3.299055931799993</v>
       </c>
       <c r="D73">
         <v>0.8552729923473003</v>
@@ -2874,7 +2874,7 @@
         <v>247</v>
       </c>
       <c r="C74">
-        <v>9.973873612951</v>
+        <v>3.254900263385381</v>
       </c>
       <c r="D74">
         <v>0.8530930344860208</v>
@@ -2894,7 +2894,7 @@
         <v>248</v>
       </c>
       <c r="C75">
-        <v>7.581514555910898</v>
+        <v>2.728047516294268</v>
       </c>
       <c r="D75">
         <v>0.8198843740571373</v>
@@ -2914,7 +2914,7 @@
         <v>249</v>
       </c>
       <c r="C76">
-        <v>2.799165879838022</v>
+        <v>1.9486486817576</v>
       </c>
       <c r="D76">
         <v>0.7525117620114423</v>
@@ -2934,7 +2934,7 @@
         <v>250</v>
       </c>
       <c r="C77">
-        <v>4.514172462130598</v>
+        <v>1.853913373183046</v>
       </c>
       <c r="D77">
         <v>0.7791295119844419</v>
@@ -2954,10 +2954,10 @@
         <v>251</v>
       </c>
       <c r="C78">
-        <v>7.416275806699781</v>
+        <v>2.936822447956227</v>
       </c>
       <c r="D78">
-        <v>0.8832884257386105</v>
+        <v>0.8832884257386104</v>
       </c>
       <c r="E78">
         <v>4.132451732044209</v>
@@ -2974,7 +2974,7 @@
         <v>252</v>
       </c>
       <c r="C79">
-        <v>7.005102335598123</v>
+        <v>2.76017609313039</v>
       </c>
       <c r="D79">
         <v>0.8801081351939124</v>
@@ -2994,10 +2994,10 @@
         <v>253</v>
       </c>
       <c r="C80">
-        <v>6.650818022832434</v>
+        <v>2.37620491093015</v>
       </c>
       <c r="D80">
-        <v>0.8352401017755701</v>
+        <v>0.8352401017755698</v>
       </c>
       <c r="E80">
         <v>3.811329395517068</v>
@@ -3014,7 +3014,7 @@
         <v>254</v>
       </c>
       <c r="C81">
-        <v>3.702907549053565</v>
+        <v>2.326839185749218</v>
       </c>
       <c r="D81">
         <v>0.8388425398126079</v>
@@ -3034,7 +3034,7 @@
         <v>255</v>
       </c>
       <c r="C82">
-        <v>3.733806488864822</v>
+        <v>2.418313737753229</v>
       </c>
       <c r="D82">
         <v>0.839196715627296</v>
@@ -3054,7 +3054,7 @@
         <v>256</v>
       </c>
       <c r="C83">
-        <v>7.975747920198229</v>
+        <v>3.100251760898668</v>
       </c>
       <c r="D83">
         <v>0.888805882080558</v>
@@ -3074,7 +3074,7 @@
         <v>257</v>
       </c>
       <c r="C84">
-        <v>4.120835513337461</v>
+        <v>2.481852934434519</v>
       </c>
       <c r="D84">
         <v>0.8438483527456191</v>
@@ -3094,7 +3094,7 @@
         <v>258</v>
       </c>
       <c r="C85">
-        <v>6.944091986130763</v>
+        <v>2.566516765731497</v>
       </c>
       <c r="D85">
         <v>0.8306541800722891</v>
@@ -3114,16 +3114,16 @@
         <v>259</v>
       </c>
       <c r="C86">
-        <v>8.771168861288048</v>
+        <v>3.056345058572826</v>
       </c>
       <c r="D86">
-        <v>0.8375782644215243</v>
+        <v>0.8375782644215244</v>
       </c>
       <c r="E86">
         <v>3.496761329753464</v>
       </c>
       <c r="F86">
-        <v>0.9020211399967329</v>
+        <v>0.9020211399967328</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3134,10 +3134,10 @@
         <v>260</v>
       </c>
       <c r="C87">
-        <v>9.698596495290152</v>
+        <v>3.208679057311894</v>
       </c>
       <c r="D87">
-        <v>0.9392270356994367</v>
+        <v>0.9392270356994364</v>
       </c>
       <c r="E87">
         <v>4.274381044251968</v>
@@ -3154,7 +3154,7 @@
         <v>261</v>
       </c>
       <c r="C88">
-        <v>8.805437686383446</v>
+        <v>3.058223447884592</v>
       </c>
       <c r="D88">
         <v>0.9011609927804745</v>
@@ -3174,7 +3174,7 @@
         <v>262</v>
       </c>
       <c r="C89">
-        <v>9.891249114691803</v>
+        <v>3.348592838791092</v>
       </c>
       <c r="D89">
         <v>0.913300864600727</v>
@@ -3194,7 +3194,7 @@
         <v>263</v>
       </c>
       <c r="C90">
-        <v>8.565015411364746</v>
+        <v>3.200712221754851</v>
       </c>
       <c r="D90">
         <v>0.896143734205297</v>
@@ -3214,10 +3214,10 @@
         <v>264</v>
       </c>
       <c r="C91">
-        <v>8.408220767755598</v>
+        <v>3.185720080574611</v>
       </c>
       <c r="D91">
-        <v>0.8951036819761801</v>
+        <v>0.8951036819761802</v>
       </c>
       <c r="E91">
         <v>3.613837106051415</v>
@@ -3234,10 +3234,10 @@
         <v>265</v>
       </c>
       <c r="C92">
-        <v>8.408220767755598</v>
+        <v>3.185720080574611</v>
       </c>
       <c r="D92">
-        <v>0.8951036819761801</v>
+        <v>0.8951036819761802</v>
       </c>
       <c r="E92">
         <v>3.531540867304834</v>
@@ -3254,7 +3254,7 @@
         <v>266</v>
       </c>
       <c r="C93">
-        <v>4.798116584502324</v>
+        <v>1.928842172357548</v>
       </c>
       <c r="D93">
         <v>0.7808980714697377</v>
@@ -3274,7 +3274,7 @@
         <v>267</v>
       </c>
       <c r="C94">
-        <v>4.384073332283455</v>
+        <v>1.806387839987392</v>
       </c>
       <c r="D94">
         <v>0.7170408634039275</v>
@@ -3294,7 +3294,7 @@
         <v>268</v>
       </c>
       <c r="C95">
-        <v>4.801063764394621</v>
+        <v>2.191306017749429</v>
       </c>
       <c r="D95">
         <v>0.764277770027277</v>
@@ -3314,7 +3314,7 @@
         <v>269</v>
       </c>
       <c r="C96">
-        <v>8.671201710065185</v>
+        <v>3.038488555555078</v>
       </c>
       <c r="D96">
         <v>0.8386630856357117</v>
@@ -3334,13 +3334,13 @@
         <v>270</v>
       </c>
       <c r="C97">
-        <v>9.661713555656625</v>
+        <v>3.204395992566103</v>
       </c>
       <c r="D97">
         <v>0.7750519209055904</v>
       </c>
       <c r="E97">
-        <v>3.367973578301096</v>
+        <v>3.367973578301095</v>
       </c>
       <c r="F97">
         <v>0.8392527015559978</v>
@@ -3354,7 +3354,7 @@
         <v>271</v>
       </c>
       <c r="C98">
-        <v>7.454071838868851</v>
+        <v>2.683181886083076</v>
       </c>
       <c r="D98">
         <v>0.8038936693351414</v>
@@ -3374,7 +3374,7 @@
         <v>272</v>
       </c>
       <c r="C99">
-        <v>8.151442819891038</v>
+        <v>2.797670436349738</v>
       </c>
       <c r="D99">
         <v>0.8169343590042834</v>
@@ -3394,7 +3394,7 @@
         <v>273</v>
       </c>
       <c r="C100">
-        <v>8.408220767755598</v>
+        <v>3.18572008057461</v>
       </c>
       <c r="D100">
         <v>0.8951036819761801</v>
@@ -3414,7 +3414,7 @@
         <v>274</v>
       </c>
       <c r="C101">
-        <v>8.318261625923702</v>
+        <v>2.714016553641254</v>
       </c>
       <c r="D101">
         <v>0.8207659853322855</v>
@@ -3434,10 +3434,10 @@
         <v>275</v>
       </c>
       <c r="C102">
-        <v>8.495966728768458</v>
+        <v>3.186645202529236</v>
       </c>
       <c r="D102">
-        <v>0.8951036819761802</v>
+        <v>0.8951036819761801</v>
       </c>
       <c r="E102">
         <v>4.063376298918186</v>
@@ -3454,7 +3454,7 @@
         <v>276</v>
       </c>
       <c r="C103">
-        <v>5.422566312107103</v>
+        <v>2.493411195740904</v>
       </c>
       <c r="D103">
         <v>0.8612463133413464</v>
@@ -3474,7 +3474,7 @@
         <v>277</v>
       </c>
       <c r="C104">
-        <v>10.81688251265996</v>
+        <v>3.412902874198151</v>
       </c>
       <c r="D104">
         <v>0.9263186596497075</v>
@@ -3494,10 +3494,10 @@
         <v>278</v>
       </c>
       <c r="C105">
-        <v>8.408220767755598</v>
+        <v>3.18572008057461</v>
       </c>
       <c r="D105">
-        <v>0.8951036819761801</v>
+        <v>0.8951036819761803</v>
       </c>
       <c r="E105">
         <v>3.531540867304834</v>
@@ -3514,7 +3514,7 @@
         <v>279</v>
       </c>
       <c r="C106">
-        <v>8.320692937026747</v>
+        <v>3.098192249845764</v>
       </c>
       <c r="D106">
         <v>0.8951036819761802</v>
@@ -3534,7 +3534,7 @@
         <v>280</v>
       </c>
       <c r="C107">
-        <v>6.462448791573429</v>
+        <v>2.239855817442575</v>
       </c>
       <c r="D107">
         <v>0.8305904324391856</v>
@@ -3554,7 +3554,7 @@
         <v>281</v>
       </c>
       <c r="C108">
-        <v>8.712959270487559</v>
+        <v>2.751635089887479</v>
       </c>
       <c r="D108">
         <v>0.8395202551442228</v>
@@ -3574,7 +3574,7 @@
         <v>282</v>
       </c>
       <c r="C109">
-        <v>6.226621116654749</v>
+        <v>2.628648202606779</v>
       </c>
       <c r="D109">
         <v>0.870614777446813</v>
@@ -3594,16 +3594,16 @@
         <v>283</v>
       </c>
       <c r="C110">
-        <v>7.682122653870912</v>
+        <v>3.016502660984174</v>
       </c>
       <c r="D110">
-        <v>0.8864232749375225</v>
+        <v>0.8982295634772851</v>
       </c>
       <c r="E110">
-        <v>3.46241194950705</v>
+        <v>5.038028042863409</v>
       </c>
       <c r="F110">
-        <v>0.9499906220686711</v>
+        <v>0.9740805099705897</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3614,16 +3614,16 @@
         <v>284</v>
       </c>
       <c r="C111">
-        <v>8.278522378197913</v>
+        <v>3.066515349273393</v>
       </c>
       <c r="D111">
-        <v>0.893553154861331</v>
+        <v>0.8864232749375225</v>
       </c>
       <c r="E111">
-        <v>3.529616766400748</v>
+        <v>3.46241194950705</v>
       </c>
       <c r="F111">
-        <v>0.9575624213031807</v>
+        <v>0.9499906220686711</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3634,16 +3634,16 @@
         <v>285</v>
       </c>
       <c r="C112">
-        <v>6.518667786216635</v>
+        <v>3.16442728090776</v>
       </c>
       <c r="D112">
-        <v>0.8125172361487506</v>
+        <v>0.893553154861331</v>
       </c>
       <c r="E112">
-        <v>3.491241699695044</v>
+        <v>3.529616766400748</v>
       </c>
       <c r="F112">
-        <v>0.8774278595722728</v>
+        <v>0.9575624213031807</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3654,16 +3654,16 @@
         <v>286</v>
       </c>
       <c r="C113">
-        <v>5.174369442310693</v>
+        <v>2.678570367506081</v>
       </c>
       <c r="D113">
-        <v>0.8564434165511933</v>
+        <v>0.8125172361487506</v>
       </c>
       <c r="E113">
-        <v>3.698929427086747</v>
+        <v>3.491241699695044</v>
       </c>
       <c r="F113">
-        <v>0.9222476631609122</v>
+        <v>0.8774278595722728</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3674,16 +3674,16 @@
         <v>287</v>
       </c>
       <c r="C114">
-        <v>4.838625725303499</v>
+        <v>2.654813346420819</v>
       </c>
       <c r="D114">
-        <v>0.7566988175493602</v>
+        <v>0.8564434165511933</v>
       </c>
       <c r="E114">
-        <v>3.031518441241953</v>
+        <v>3.698929427086747</v>
       </c>
       <c r="F114">
-        <v>0.8180620090970189</v>
+        <v>0.9222476631609122</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3694,16 +3694,16 @@
         <v>288</v>
       </c>
       <c r="C115">
-        <v>2.157904519630951</v>
+        <v>1.845752991401673</v>
       </c>
       <c r="D115">
-        <v>0.7660630236475754</v>
+        <v>0.7566988175493601</v>
       </c>
       <c r="E115">
-        <v>2.61479720900857</v>
+        <v>3.031518441241953</v>
       </c>
       <c r="F115">
-        <v>0.823672283502012</v>
+        <v>0.8180620090970189</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3714,16 +3714,16 @@
         <v>289</v>
       </c>
       <c r="C116">
-        <v>5.83929494878394</v>
+        <v>1.517204395468299</v>
       </c>
       <c r="D116">
-        <v>0.8659826514124419</v>
+        <v>0.7660630236475752</v>
       </c>
       <c r="E116">
-        <v>5.240649431186528</v>
+        <v>2.61479720900857</v>
       </c>
       <c r="F116">
-        <v>0.9438311570469117</v>
+        <v>0.823672283502012</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3734,16 +3734,16 @@
         <v>290</v>
       </c>
       <c r="C117">
-        <v>3.882075199345663</v>
+        <v>2.652884545381513</v>
       </c>
       <c r="D117">
-        <v>0.840802580382611</v>
+        <v>0.8659826514124419</v>
       </c>
       <c r="E117">
-        <v>4.000434081623447</v>
+        <v>5.240649431186528</v>
       </c>
       <c r="F117">
-        <v>0.9091789239611355</v>
+        <v>0.9438311570469117</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3754,16 +3754,16 @@
         <v>291</v>
       </c>
       <c r="C118">
-        <v>7.85764756858931</v>
+        <v>2.44265525779752</v>
       </c>
       <c r="D118">
-        <v>0.8267570686592114</v>
+        <v>0.840802580382611</v>
       </c>
       <c r="E118">
-        <v>4.158964864135972</v>
+        <v>4.000434081623447</v>
       </c>
       <c r="F118">
-        <v>0.8969544120046029</v>
+        <v>0.9091789239611355</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3774,16 +3774,16 @@
         <v>292</v>
       </c>
       <c r="C119">
-        <v>3.930302780150556</v>
+        <v>2.903443221615279</v>
       </c>
       <c r="D119">
-        <v>0.8415707639381759</v>
+        <v>0.8267570686592113</v>
       </c>
       <c r="E119">
-        <v>3.839097857729196</v>
+        <v>4.158964864135972</v>
       </c>
       <c r="F119">
-        <v>0.9086648500076391</v>
+        <v>0.8969544120046029</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3794,16 +3794,16 @@
         <v>293</v>
       </c>
       <c r="C120">
-        <v>3.569550440286211</v>
+        <v>2.450572859704511</v>
       </c>
       <c r="D120">
-        <v>0.7814020157583432</v>
+        <v>0.8415707639381759</v>
       </c>
       <c r="E120">
-        <v>3.82691131000153</v>
+        <v>3.839097857729196</v>
       </c>
       <c r="F120">
-        <v>0.8487828676733087</v>
+        <v>0.9086648500076391</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3814,16 +3814,16 @@
         <v>294</v>
       </c>
       <c r="C121">
-        <v>7.775494399294534</v>
+        <v>1.794868468427659</v>
       </c>
       <c r="D121">
-        <v>0.8864232749375225</v>
+        <v>0.7814020157583432</v>
       </c>
       <c r="E121">
-        <v>4.136703068761483</v>
+        <v>3.82691131000153</v>
       </c>
       <c r="F121">
-        <v>0.9553099720474491</v>
+        <v>0.8487828676733087</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3834,16 +3834,16 @@
         <v>295</v>
       </c>
       <c r="C122">
-        <v>9.477230896719476</v>
+        <v>3.067499784917335</v>
       </c>
       <c r="D122">
-        <v>0.910270627622775</v>
+        <v>0.8864232749375225</v>
       </c>
       <c r="E122">
-        <v>3.72830213634668</v>
+        <v>4.136703068761483</v>
       </c>
       <c r="F122">
-        <v>0.9763369541446756</v>
+        <v>0.9553099720474491</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3854,16 +3854,16 @@
         <v>296</v>
       </c>
       <c r="C123">
-        <v>6.758120218429642</v>
+        <v>3.186059319098888</v>
       </c>
       <c r="D123">
-        <v>0.8768353345840207</v>
+        <v>0.910270627622775</v>
       </c>
       <c r="E123">
-        <v>4.171828617230183</v>
+        <v>3.72830213634668</v>
       </c>
       <c r="F123">
-        <v>0.9462873815838656</v>
+        <v>0.9763369541446756</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3874,16 +3874,16 @@
         <v>297</v>
       </c>
       <c r="C124">
-        <v>8.344001063831683</v>
+        <v>2.714273380172231</v>
       </c>
       <c r="D124">
-        <v>0.869859233758872</v>
+        <v>0.8768353345840206</v>
       </c>
       <c r="E124">
-        <v>3.144456187334026</v>
+        <v>4.171828617230183</v>
       </c>
       <c r="F124">
-        <v>0.9327436851349123</v>
+        <v>0.9462873815838656</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3894,16 +3894,16 @@
         <v>298</v>
       </c>
       <c r="C125">
-        <v>8.914975203052501</v>
+        <v>2.514890811342783</v>
       </c>
       <c r="D125">
-        <v>0.9011618643111927</v>
+        <v>0.8698592337588721</v>
       </c>
       <c r="E125">
-        <v>3.539058668184475</v>
+        <v>3.144456187334026</v>
       </c>
       <c r="F125">
-        <v>0.9651514433349522</v>
+        <v>0.9327436851349123</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3914,16 +3914,16 @@
         <v>299</v>
       </c>
       <c r="C126">
-        <v>3.649545038973724</v>
+        <v>3.268914796467869</v>
       </c>
       <c r="D126">
-        <v>0.7675839075920117</v>
+        <v>0.9011618643111927</v>
       </c>
       <c r="E126">
-        <v>3.266932190235052</v>
+        <v>3.539058668184475</v>
       </c>
       <c r="F126">
-        <v>0.8303189080853859</v>
+        <v>0.9651514433349522</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3934,16 +3934,16 @@
         <v>300</v>
       </c>
       <c r="C127">
-        <v>2.804877807251718</v>
+        <v>1.670105117493497</v>
       </c>
       <c r="D127">
-        <v>0.828116457048482</v>
+        <v>0.7675839075920117</v>
       </c>
       <c r="E127">
-        <v>3.760877100150769</v>
+        <v>3.266932190235052</v>
       </c>
       <c r="F127">
-        <v>0.8947599984239355</v>
+        <v>0.8303189080853859</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3954,16 +3954,16 @@
         <v>301</v>
       </c>
       <c r="C128">
-        <v>7.220123494600619</v>
+        <v>2.265809975834257</v>
       </c>
       <c r="D128">
-        <v>0.8160039750785297</v>
+        <v>0.828116457048482</v>
       </c>
       <c r="E128">
-        <v>3.655145590007987</v>
+        <v>3.760877100150769</v>
       </c>
       <c r="F128">
-        <v>0.8822343585294855</v>
+        <v>0.8947599984239355</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3974,16 +3974,16 @@
         <v>302</v>
       </c>
       <c r="C129">
-        <v>4.762442493746299</v>
+        <v>2.794582275938882</v>
       </c>
       <c r="D129">
-        <v>0.7940185127572373</v>
+        <v>0.81600397507853</v>
       </c>
       <c r="E129">
-        <v>3.781962375503493</v>
+        <v>3.655145590007987</v>
       </c>
       <c r="F129">
-        <v>0.8606300202748872</v>
+        <v>0.8822343585294855</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3994,16 +3994,16 @@
         <v>303</v>
       </c>
       <c r="C130">
-        <v>9.391335714138966</v>
+        <v>1.988341116086882</v>
       </c>
       <c r="D130">
-        <v>0.8638774724881113</v>
+        <v>0.7940185127572373</v>
       </c>
       <c r="E130">
-        <v>4.038997983843318</v>
+        <v>3.781962375503493</v>
       </c>
       <c r="F130">
-        <v>0.9343308318447019</v>
+        <v>0.8606300202748872</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4014,16 +4014,16 @@
         <v>304</v>
       </c>
       <c r="C131">
-        <v>7.471806514006397</v>
+        <v>2.836064416988693</v>
       </c>
       <c r="D131">
-        <v>0.9289230652455772</v>
+        <v>0.8638774724881113</v>
       </c>
       <c r="E131">
-        <v>3.934663770555487</v>
+        <v>4.038997983843318</v>
       </c>
       <c r="F131">
-        <v>0.9960352041637394</v>
+        <v>0.9343308318447019</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4034,16 +4034,16 @@
         <v>305</v>
       </c>
       <c r="C132">
-        <v>8.408220767755598</v>
+        <v>2.74266646587061</v>
       </c>
       <c r="D132">
-        <v>0.8951036819761801</v>
+        <v>0.9289230652455772</v>
       </c>
       <c r="E132">
-        <v>3.531540867304834</v>
+        <v>3.934663770555487</v>
       </c>
       <c r="F132">
-        <v>0.9591089364530876</v>
+        <v>0.9960352041637394</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4054,16 +4054,16 @@
         <v>306</v>
       </c>
       <c r="C133">
-        <v>10.57324360815445</v>
+        <v>3.18572008057461</v>
       </c>
       <c r="D133">
-        <v>0.8478513880016191</v>
+        <v>0.8951036819761802</v>
       </c>
       <c r="E133">
-        <v>4.456930133419752</v>
+        <v>3.531540867304834</v>
       </c>
       <c r="F133">
-        <v>0.9206564154401947</v>
+        <v>0.9591089364530876</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4074,16 +4074,16 @@
         <v>307</v>
       </c>
       <c r="C134">
-        <v>7.682122653870912</v>
+        <v>3.352902392404109</v>
       </c>
       <c r="D134">
-        <v>0.8864232749375225</v>
+        <v>0.8478513880016191</v>
       </c>
       <c r="E134">
-        <v>3.520769060174879</v>
+        <v>4.456930133419752</v>
       </c>
       <c r="F134">
-        <v>0.9504509898334665</v>
+        <v>0.9206564154401947</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4094,16 +4094,16 @@
         <v>308</v>
       </c>
       <c r="C135">
-        <v>6.365589948931241</v>
+        <v>3.066515349273393</v>
       </c>
       <c r="D135">
-        <v>0.8700033826319667</v>
+        <v>0.8864232749375225</v>
       </c>
       <c r="E135">
-        <v>3.500393067180267</v>
+        <v>3.520769060174879</v>
       </c>
       <c r="F135">
-        <v>0.9340735837454434</v>
+        <v>0.9504509898334665</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4114,16 +4114,16 @@
         <v>309</v>
       </c>
       <c r="C136">
-        <v>2.081882865456086</v>
+        <v>2.841627719838</v>
       </c>
       <c r="D136">
-        <v>0.7565557800761872</v>
+        <v>0.8700033826319667</v>
       </c>
       <c r="E136">
-        <v>3.09607464720889</v>
+        <v>3.500393067180267</v>
       </c>
       <c r="F136">
-        <v>0.8167963719128366</v>
+        <v>0.9340735837454434</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4134,16 +4134,16 @@
         <v>310</v>
       </c>
       <c r="C137">
-        <v>4.485761238577296</v>
+        <v>1.406530728698381</v>
       </c>
       <c r="D137">
-        <v>0.7587071147657095</v>
+        <v>0.7565557800761872</v>
       </c>
       <c r="E137">
-        <v>3.38693745801857</v>
+        <v>3.09607464720889</v>
       </c>
       <c r="F137">
-        <v>0.8224986809526815</v>
+        <v>0.8167963719128367</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4154,16 +4154,16 @@
         <v>311</v>
       </c>
       <c r="C138">
-        <v>4.751106244094147</v>
+        <v>1.918974275019009</v>
       </c>
       <c r="D138">
-        <v>0.8486228766552896</v>
+        <v>0.7587071147657095</v>
       </c>
       <c r="E138">
-        <v>3.729393693331801</v>
+        <v>3.38693745801857</v>
       </c>
       <c r="F138">
-        <v>0.914185011784297</v>
+        <v>0.8224986809526815</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4174,16 +4174,16 @@
         <v>312</v>
       </c>
       <c r="C139">
-        <v>8.478407494749954</v>
+        <v>1.960934578846674</v>
       </c>
       <c r="D139">
-        <v>0.8951036819761801</v>
+        <v>0.8486228766552896</v>
       </c>
       <c r="E139">
-        <v>3.531540867304834</v>
+        <v>3.729393693331801</v>
       </c>
       <c r="F139">
-        <v>0.9591089364530877</v>
+        <v>0.914185011784297</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4194,16 +4194,16 @@
         <v>313</v>
       </c>
       <c r="C140">
-        <v>10.1153764857764</v>
+        <v>3.186460072265581</v>
       </c>
       <c r="D140">
-        <v>0.9173019026313048</v>
+        <v>0.8951036819761802</v>
       </c>
       <c r="E140">
-        <v>3.353404588305841</v>
+        <v>3.531540867304834</v>
       </c>
       <c r="F140">
-        <v>0.9796271284700209</v>
+        <v>0.9591089364530877</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4214,16 +4214,16 @@
         <v>314</v>
       </c>
       <c r="C141">
-        <v>8.46601060299122</v>
+        <v>3.286013697352379</v>
       </c>
       <c r="D141">
-        <v>0.8951036819761801</v>
+        <v>0.9173019026313048</v>
       </c>
       <c r="E141">
-        <v>3.531540867304834</v>
+        <v>3.353404588305841</v>
       </c>
       <c r="F141">
-        <v>0.9591089364530876</v>
+        <v>0.9796271284700209</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4234,16 +4234,16 @@
         <v>315</v>
       </c>
       <c r="C142">
-        <v>6.00345728713037</v>
+        <v>3.186329369534621</v>
       </c>
       <c r="D142">
-        <v>0.8663550522189059</v>
+        <v>0.8951036819761802</v>
       </c>
       <c r="E142">
-        <v>3.422850681961802</v>
+        <v>3.531540867304834</v>
       </c>
       <c r="F142">
-        <v>0.9298586919657152</v>
+        <v>0.9591089364530876</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4254,16 +4254,16 @@
         <v>316</v>
       </c>
       <c r="C143">
-        <v>10.37774759411352</v>
+        <v>2.790926072617118</v>
       </c>
       <c r="D143">
-        <v>0.9186491150236175</v>
+        <v>0.8663550522189059</v>
       </c>
       <c r="E143">
-        <v>3.560759181889478</v>
+        <v>3.422850681961802</v>
       </c>
       <c r="F143">
-        <v>0.9825934460564646</v>
+        <v>0.9298586919657152</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4274,16 +4274,16 @@
         <v>317</v>
       </c>
       <c r="C144">
-        <v>4.497050451906878</v>
+        <v>3.509060565334253</v>
       </c>
       <c r="D144">
-        <v>0.8511062641351126</v>
+        <v>0.9186491150236175</v>
       </c>
       <c r="E144">
-        <v>3.899337623756638</v>
+        <v>3.560759181889478</v>
       </c>
       <c r="F144">
-        <v>0.9185575493235676</v>
+        <v>0.9825934460564646</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4294,16 +4294,16 @@
         <v>318</v>
       </c>
       <c r="C145">
-        <v>9.126972021432421</v>
+        <v>2.349192454895924</v>
       </c>
       <c r="D145">
-        <v>0.9026363441583806</v>
+        <v>0.8511062641351126</v>
       </c>
       <c r="E145">
-        <v>3.540888494453432</v>
+        <v>3.899337623756638</v>
       </c>
       <c r="F145">
-        <v>0.9666221087374496</v>
+        <v>0.9185575493235676</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4314,16 +4314,16 @@
         <v>319</v>
       </c>
       <c r="C146">
-        <v>8.408220767755598</v>
+        <v>3.290099949148722</v>
       </c>
       <c r="D146">
-        <v>0.8951036819761801</v>
+        <v>0.9026363441583806</v>
       </c>
       <c r="E146">
-        <v>5.166954581862816</v>
+        <v>3.540888494453432</v>
       </c>
       <c r="F146">
-        <v>0.972010393493551</v>
+        <v>0.9666221087374496</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4334,16 +4334,16 @@
         <v>320</v>
       </c>
       <c r="C147">
-        <v>8.408220767755598</v>
+        <v>3.185720080574611</v>
       </c>
       <c r="D147">
-        <v>0.8951036819761802</v>
+        <v>0.8951036819761801</v>
       </c>
       <c r="E147">
-        <v>3.531540867304834</v>
+        <v>5.166954581862816</v>
       </c>
       <c r="F147">
-        <v>0.9591089364530876</v>
+        <v>0.972010393493551</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4354,16 +4354,16 @@
         <v>321</v>
       </c>
       <c r="C148">
-        <v>6.685537837271911</v>
+        <v>3.185720080574611</v>
       </c>
       <c r="D148">
-        <v>0.8745708895875237</v>
+        <v>0.8951036819761801</v>
       </c>
       <c r="E148">
-        <v>3.509244135684379</v>
+        <v>3.531540867304834</v>
       </c>
       <c r="F148">
-        <v>0.9386543831694774</v>
+        <v>0.9591089364530877</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4374,16 +4374,16 @@
         <v>322</v>
       </c>
       <c r="C149">
-        <v>7.941468100062787</v>
+        <v>2.817091662551796</v>
       </c>
       <c r="D149">
-        <v>0.8007794759250808</v>
+        <v>0.8745708895875236</v>
       </c>
       <c r="E149">
-        <v>4.043337706243987</v>
+        <v>3.509244135684379</v>
       </c>
       <c r="F149">
-        <v>0.8704366571168237</v>
+        <v>0.9386543831694774</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4394,16 +4394,16 @@
         <v>323</v>
       </c>
       <c r="C150">
-        <v>3.69258323714758</v>
+        <v>2.65733722048792</v>
       </c>
       <c r="D150">
-        <v>0.8387382623282122</v>
+        <v>0.8007794759250808</v>
       </c>
       <c r="E150">
-        <v>3.464601817386119</v>
+        <v>4.043337706243987</v>
       </c>
       <c r="F150">
-        <v>0.9029130805850258</v>
+        <v>0.8704366571168237</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4414,16 +4414,16 @@
         <v>324</v>
       </c>
       <c r="C151">
-        <v>8.914975203052501</v>
+        <v>2.323296093651456</v>
       </c>
       <c r="D151">
-        <v>0.9011618643111927</v>
+        <v>0.8387382623282124</v>
       </c>
       <c r="E151">
-        <v>3.539058668184475</v>
+        <v>3.464601817386119</v>
       </c>
       <c r="F151">
-        <v>0.9651514433349522</v>
+        <v>0.9029130805850258</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4434,16 +4434,16 @@
         <v>325</v>
       </c>
       <c r="C152">
-        <v>8.122960376565565</v>
+        <v>3.268914796467869</v>
       </c>
       <c r="D152">
-        <v>0.8486754038865381</v>
+        <v>0.9011618643111926</v>
       </c>
       <c r="E152">
-        <v>3.450030546924355</v>
+        <v>3.539058668184475</v>
       </c>
       <c r="F152">
-        <v>0.9130638156296491</v>
+        <v>0.9651514433349522</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -4454,16 +4454,16 @@
         <v>326</v>
       </c>
       <c r="C153">
-        <v>7.635982467983463</v>
+        <v>2.959480086961444</v>
       </c>
       <c r="D153">
-        <v>0.8884585671284384</v>
+        <v>0.8486754038865381</v>
       </c>
       <c r="E153">
-        <v>3.630186903767049</v>
+        <v>3.450030546924355</v>
       </c>
       <c r="F153">
-        <v>0.9533242671270907</v>
+        <v>0.9130638156296491</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4474,16 +4474,16 @@
         <v>327</v>
       </c>
       <c r="C154">
-        <v>6.462181334859795</v>
+        <v>2.877513945338942</v>
       </c>
       <c r="D154">
-        <v>0.767281018037426</v>
+        <v>0.8884585671284384</v>
       </c>
       <c r="E154">
-        <v>3.43942064767946</v>
+        <v>3.630186903767049</v>
       </c>
       <c r="F154">
-        <v>0.8323077323764163</v>
+        <v>0.9533242671270907</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -4494,16 +4494,16 @@
         <v>328</v>
       </c>
       <c r="C155">
-        <v>7.766353330351703</v>
+        <v>2.501648134400228</v>
       </c>
       <c r="D155">
-        <v>0.8268364322141898</v>
+        <v>0.767281018037426</v>
       </c>
       <c r="E155">
-        <v>3.680844890106498</v>
+        <v>3.43942064767946</v>
       </c>
       <c r="F155">
-        <v>0.8932455575615958</v>
+        <v>0.8323077323764163</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -4514,16 +4514,16 @@
         <v>329</v>
       </c>
       <c r="C156">
-        <v>7.460858150892616</v>
+        <v>2.899454513444653</v>
       </c>
       <c r="D156">
-        <v>0.8310560404925749</v>
+        <v>0.8268364322141898</v>
       </c>
       <c r="E156">
-        <v>3.369598254235113</v>
+        <v>3.680844890106498</v>
       </c>
       <c r="F156">
-        <v>0.893684755054714</v>
+        <v>0.8932455575615958</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4534,16 +4534,16 @@
         <v>330</v>
       </c>
       <c r="C157">
-        <v>7.22046439568309</v>
+        <v>2.506080773278655</v>
       </c>
       <c r="D157">
-        <v>0.8807936640924316</v>
+        <v>0.8310560404925749</v>
       </c>
       <c r="E157">
-        <v>4.141296730571518</v>
+        <v>3.369598254235113</v>
       </c>
       <c r="F157">
-        <v>0.9500370651267006</v>
+        <v>0.893684755054714</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4554,16 +4554,16 @@
         <v>331</v>
       </c>
       <c r="C158">
-        <v>5.843099591555666</v>
+        <v>2.902813789229372</v>
       </c>
       <c r="D158">
-        <v>0.7592112837949861</v>
+        <v>0.8807936640924316</v>
       </c>
       <c r="E158">
-        <v>4.376668536036051</v>
+        <v>4.141296730571518</v>
       </c>
       <c r="F158">
-        <v>0.8315248187201465</v>
+        <v>0.9500370651267006</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -4574,16 +4574,16 @@
         <v>332</v>
       </c>
       <c r="C159">
-        <v>8.289364100053106</v>
+        <v>2.245936608787515</v>
       </c>
       <c r="D159">
-        <v>0.8951003840153001</v>
+        <v>0.7592112837949861</v>
       </c>
       <c r="E159">
-        <v>3.488394127481176</v>
+        <v>4.376668536036051</v>
       </c>
       <c r="F159">
-        <v>0.9587653031692351</v>
+        <v>0.8315248187201465</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -4594,16 +4594,16 @@
         <v>333</v>
       </c>
       <c r="C160">
-        <v>5.529271741917282</v>
+        <v>2.972427620403966</v>
       </c>
       <c r="D160">
-        <v>0.7851771556562153</v>
+        <v>0.8951003840153001</v>
       </c>
       <c r="E160">
-        <v>3.764372080597269</v>
+        <v>3.488394127481176</v>
       </c>
       <c r="F160">
-        <v>0.8539100196633398</v>
+        <v>0.9587653031692351</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -4614,16 +4614,16 @@
         <v>334</v>
       </c>
       <c r="C161">
-        <v>3.313848571491222</v>
+        <v>2.203180231596392</v>
       </c>
       <c r="D161">
-        <v>0.8357477152795791</v>
+        <v>0.7851771556562153</v>
       </c>
       <c r="E161">
-        <v>3.331877177289577</v>
+        <v>3.764372080597269</v>
       </c>
       <c r="F161">
-        <v>0.8989125088565475</v>
+        <v>0.8539100196633398</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -4634,16 +4634,16 @@
         <v>335</v>
       </c>
       <c r="C162">
-        <v>8.082571271905614</v>
+        <v>2.133098243681575</v>
       </c>
       <c r="D162">
-        <v>1.157271903863976</v>
+        <v>0.8357477152795791</v>
       </c>
       <c r="E162">
-        <v>3.731000483626067</v>
+        <v>3.331877177289577</v>
       </c>
       <c r="F162">
-        <v>1.22004102374715</v>
+        <v>0.8989125088565475</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -4654,16 +4654,16 @@
         <v>336</v>
       </c>
       <c r="C163">
-        <v>4.7521272594199</v>
+        <v>2.952682551483019</v>
       </c>
       <c r="D163">
-        <v>0.7914026999005037</v>
+        <v>1.157271903863976</v>
       </c>
       <c r="E163">
-        <v>4.00398415801732</v>
+        <v>3.731000483626067</v>
       </c>
       <c r="F163">
-        <v>0.8604184698801408</v>
+        <v>1.22004102374715</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -4674,16 +4674,16 @@
         <v>337</v>
       </c>
       <c r="C164">
-        <v>7.584991056144146</v>
+        <v>2.496842508696638</v>
       </c>
       <c r="D164">
-        <v>0.886648792574685</v>
+        <v>0.7914026999005038</v>
       </c>
       <c r="E164">
-        <v>3.948021263222629</v>
+        <v>4.00398415801732</v>
       </c>
       <c r="F164">
-        <v>0.9543665416719163</v>
+        <v>0.8604184698801408</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -4694,16 +4694,16 @@
         <v>338</v>
       </c>
       <c r="C165">
-        <v>7.682122653870912</v>
+        <v>2.853292985815116</v>
       </c>
       <c r="D165">
-        <v>0.8864232749375225</v>
+        <v>0.886648792574685</v>
       </c>
       <c r="E165">
-        <v>3.520769060174879</v>
+        <v>3.948021263222629</v>
       </c>
       <c r="F165">
-        <v>0.9504509898334665</v>
+        <v>0.9543665416719163</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -4714,16 +4714,16 @@
         <v>339</v>
       </c>
       <c r="C166">
-        <v>11.01595211209944</v>
+        <v>3.066515349273393</v>
       </c>
       <c r="D166">
-        <v>0.925401310676749</v>
+        <v>0.8864232749375225</v>
       </c>
       <c r="E166">
-        <v>3.569138178722839</v>
+        <v>3.520769060174879</v>
       </c>
       <c r="F166">
-        <v>0.9893281702839757</v>
+        <v>0.9504509898334665</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -4734,16 +4734,16 @@
         <v>340</v>
       </c>
       <c r="C167">
-        <v>11.08637723558552</v>
+        <v>3.602559168445163</v>
       </c>
       <c r="D167">
-        <v>0.9308324833340215</v>
+        <v>0.925401310676749</v>
       </c>
       <c r="E167">
-        <v>3.722181273125889</v>
+        <v>3.569138178722839</v>
       </c>
       <c r="F167">
-        <v>0.9921327457125053</v>
+        <v>0.9893281702839757</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -4754,16 +4754,16 @@
         <v>341</v>
       </c>
       <c r="C168">
-        <v>3.936589843621361</v>
+        <v>3.252849452411428</v>
       </c>
       <c r="D168">
-        <v>0.8433434520545927</v>
+        <v>0.9308324833340215</v>
       </c>
       <c r="E168">
-        <v>4.745313245750898</v>
+        <v>3.722181273125889</v>
       </c>
       <c r="F168">
-        <v>0.9172011435598049</v>
+        <v>0.9921327457125053</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -4774,16 +4774,16 @@
         <v>342</v>
       </c>
       <c r="C169">
-        <v>7.992595780956194</v>
+        <v>2.240378102135467</v>
       </c>
       <c r="D169">
-        <v>0.890324578453153</v>
+        <v>0.8433434520545927</v>
       </c>
       <c r="E169">
-        <v>4.915940222151752</v>
+        <v>4.745313245750898</v>
       </c>
       <c r="F169">
-        <v>0.9653102378643927</v>
+        <v>0.9172011435598049</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -4794,16 +4794,16 @@
         <v>343</v>
       </c>
       <c r="C170">
-        <v>8.533839050499736</v>
+        <v>3.033384989453151</v>
       </c>
       <c r="D170">
-        <v>0.8982295634772851</v>
+        <v>0.8903245784531529</v>
       </c>
       <c r="E170">
-        <v>5.038028042863409</v>
+        <v>4.915940222151752</v>
       </c>
       <c r="F170">
-        <v>0.9740805099705897</v>
+        <v>0.9653102378643927</v>
       </c>
     </row>
   </sheetData>
